--- a/debug/judgements_intro/excel_overviews/gpt-4.1_vs_gemini-1.5-flash/Qwen3-Next-80B-A3B-Instruct/metrics_default_vs_aae.xlsx
+++ b/debug/judgements_intro/excel_overviews/gpt-4.1_vs_gemini-1.5-flash/Qwen3-Next-80B-A3B-Instruct/metrics_default_vs_aae.xlsx
@@ -420,25 +420,25 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>0.9019607843137255</v>
+        <v>0.9108910891089109</v>
       </c>
       <c r="B2">
         <v>0</v>
       </c>
       <c r="C2">
-        <v>0.75177304964539</v>
+        <v>0.7730496453900709</v>
       </c>
       <c r="D2">
-        <v>0.2755905511811024</v>
+        <v>0.2580645161290323</v>
       </c>
       <c r="E2">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="F2">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="G2">
-        <v>14</v>
+        <v>17</v>
       </c>
     </row>
   </sheetData>
